--- a/Hardware/production/bom_with link.xlsx
+++ b/Hardware/production/bom_with link.xlsx
@@ -1,26 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\sf-motion\Hardware\production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{97B80BDE-BEFC-4CCA-B0A5-FEB2FB30C0A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFD23E8F-DA0E-4D6C-9D07-88F26B537407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{0ECE070C-B3C0-4610-AB94-0DB4F15A23CE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{0ECE070C-B3C0-4610-AB94-0DB4F15A23CE}"/>
   </bookViews>
   <sheets>
     <sheet name="bom" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="212">
   <si>
     <t>Designator</t>
   </si>
@@ -653,6 +667,9 @@
   </si>
   <si>
     <t>https://item.taobao.com/item.htm?spm=a1z0d.6639537%2F202410.item.d973872188161.447d7484y2F3Il&amp;id=973872188161&amp;from=cart&amp;skuId=6093104858737&amp;mi_id=00005VLxnAPrvXiGMF58yebMaPwGuAFHE7U9En2pE3D1R3k&amp;upStreamPrice=1350</t>
+  </si>
+  <si>
+    <t>CHANGE TO 2512</t>
   </si>
 </sst>
 </file>
@@ -2167,6 +2184,9 @@
       <c r="E28" t="s">
         <v>95</v>
       </c>
+      <c r="G28" s="2" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
